--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.85006</v>
+        <v>16.9956</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76396</v>
+        <v>16.80925</v>
       </c>
       <c r="E2" t="n">
-        <v>16.64979</v>
+        <v>16.95636</v>
       </c>
       <c r="F2" t="n">
-        <v>43.24766</v>
+        <v>41.87611</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04981</v>
+        <v>0.05077</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83654</v>
+        <v>1.83989</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.00338</v>
+        <v>17.03779</v>
       </c>
       <c r="D3" t="n">
-        <v>16.78614</v>
+        <v>16.49076</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04098</v>
+        <v>16.60511</v>
       </c>
       <c r="F3" t="n">
-        <v>42.65054</v>
+        <v>42.99526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05044</v>
+        <v>0.05177</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83403</v>
+        <v>1.83702</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.06237</v>
+        <v>16.96958</v>
       </c>
       <c r="D4" t="n">
-        <v>16.34547</v>
+        <v>16.64111</v>
       </c>
       <c r="E4" t="n">
-        <v>16.89332</v>
+        <v>16.68593</v>
       </c>
       <c r="F4" t="n">
-        <v>42.56878</v>
+        <v>41.8733</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0511</v>
+        <v>0.05106</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82402</v>
+        <v>1.8421</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8793</v>
+        <v>16.57475</v>
       </c>
       <c r="D6" t="n">
-        <v>15.85758</v>
+        <v>16.46265</v>
       </c>
       <c r="E6" t="n">
-        <v>16.51099</v>
+        <v>16.50888</v>
       </c>
       <c r="F6" t="n">
-        <v>21.57339</v>
+        <v>21.29594</v>
       </c>
       <c r="G6" t="n">
-        <v>34.24034</v>
+        <v>34.30923</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.6161</v>
+        <v>16.75373</v>
       </c>
       <c r="D7" t="n">
-        <v>15.91625</v>
+        <v>16.08972</v>
       </c>
       <c r="E7" t="n">
-        <v>16.05547</v>
+        <v>16.3777</v>
       </c>
       <c r="F7" t="n">
-        <v>21.77748</v>
+        <v>22.0781</v>
       </c>
       <c r="G7" t="n">
-        <v>34.20637</v>
+        <v>34.30896</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.58087</v>
+        <v>17.0228</v>
       </c>
       <c r="D8" t="n">
-        <v>16.0402</v>
+        <v>15.848</v>
       </c>
       <c r="E8" t="n">
-        <v>16.69242</v>
+        <v>16.39088</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81169</v>
+        <v>22.05564</v>
       </c>
       <c r="G8" t="n">
-        <v>34.95127</v>
+        <v>34.42829</v>
       </c>
     </row>
   </sheetData>
